--- a/artfynd/A 5288-2023 artfynd.xlsx
+++ b/artfynd/A 5288-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5288-2023 artfynd.xlsx
+++ b/artfynd/A 5288-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,234 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115070786</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56453</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>762510</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7451176</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115057240</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79556</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>762511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7451030</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5288-2023 artfynd.xlsx
+++ b/artfynd/A 5288-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>61642759</v>
       </c>
       <c r="B2" t="n">
-        <v>89332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762446.8197080747</v>
+        <v>762447</v>
       </c>
       <c r="R2" t="n">
-        <v>7451168.287614156</v>
+        <v>7451168</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2016-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,12 +780,7 @@
         <v>98840813</v>
       </c>
       <c r="B3" t="n">
-        <v>86298</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762481.3812135183</v>
+        <v>762481</v>
       </c>
       <c r="R3" t="n">
-        <v>7451128.094264563</v>
+        <v>7451128</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,19 +852,9 @@
           <t>2020-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -920,12 +890,7 @@
         <v>115057240</v>
       </c>
       <c r="B4" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,12 +997,7 @@
         <v>115070786</v>
       </c>
       <c r="B5" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,6 +1102,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115057943</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>762516</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7451023</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5288-2023 artfynd.xlsx
+++ b/artfynd/A 5288-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61642759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98840813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115057240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115070786</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,8 +1234,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115057943</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>